--- a/MBG01D.xlsx
+++ b/MBG01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="117">
   <si>
     <t/>
   </si>
@@ -70,6 +70,42 @@
     <t>11</t>
   </si>
   <si>
+    <t>20062961</t>
+  </si>
+  <si>
+    <t>ANAKRAJA BRS KRSTL5K</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20142055</t>
+  </si>
+  <si>
+    <t>TOPI KOKI SETRA RYL5</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20142107</t>
+  </si>
+  <si>
+    <t>TAR BERAS KHUSUS 5KG</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20142006</t>
+  </si>
+  <si>
+    <t>PTRI KOKI BRS KH 5KG</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>20128415</t>
   </si>
   <si>
@@ -106,39 +142,42 @@
     <t>LARST BRS SLYP SPR 5</t>
   </si>
   <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20139532</t>
+  </si>
+  <si>
+    <t>A/R BRS KHS PLN WG5</t>
+  </si>
+  <si>
     <t>7</t>
   </si>
   <si>
-    <t>20139532</t>
-  </si>
-  <si>
-    <t>A/R BRS KHS PLN WG5</t>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20106876</t>
+  </si>
+  <si>
+    <t>UDG D/KOKI BRS PRM 5</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20106876</t>
-  </si>
-  <si>
-    <t>UDG D/KOKI BRS PRM 5</t>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20084982</t>
+  </si>
+  <si>
+    <t>D/KOKI BRAS SHT 5KG</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20084982</t>
-  </si>
-  <si>
-    <t>D/KOKI BRAS SHT 5KG</t>
-  </si>
-  <si>
     <t>20000412</t>
   </si>
   <si>
@@ -193,9 +232,6 @@
     <t>LARST BRS SLP SPR2.5</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>20141513</t>
   </si>
   <si>
@@ -230,9 +266,6 @@
   </si>
   <si>
     <t>IDM GULA BATU 225</t>
-  </si>
-  <si>
-    <t>6</t>
   </si>
   <si>
     <t>20103654</t>
@@ -721,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -863,13 +896,13 @@
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -883,61 +916,61 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -946,18 +979,18 @@
         <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -966,10 +999,10 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -989,15 +1022,15 @@
         <v>38</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1006,7 +1039,7 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1014,39 +1047,39 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F15" s="1" t="s">
-        <v>44</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>47</v>
@@ -1063,110 +1096,110 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>38</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>9</v>
@@ -1174,19 +1207,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>9</v>
@@ -1194,70 +1227,70 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>69</v>
+        <v>24</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1266,7 +1299,7 @@
         <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>9</v>
@@ -1274,10 +1307,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1286,10 +1319,10 @@
         <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>76</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1306,10 +1339,10 @@
         <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1326,18 +1359,18 @@
         <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1346,10 +1379,10 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>84</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1363,193 +1396,273 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>47</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>69</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="E41" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F41" s="1" t="s">
-        <v>47</v>
+      <c r="F45" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/MBG01D.xlsx
+++ b/MBG01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="121">
   <si>
     <t/>
   </si>
@@ -178,6 +178,12 @@
     <t>9</t>
   </si>
   <si>
+    <t>20142264</t>
+  </si>
+  <si>
+    <t>LAHAP LELE BRS PRM 5</t>
+  </si>
+  <si>
     <t>20000412</t>
   </si>
   <si>
@@ -362,6 +368,12 @@
   </si>
   <si>
     <t>LRST GULA KRSTL 1KG</t>
+  </si>
+  <si>
+    <t>20103543</t>
+  </si>
+  <si>
+    <t>FS GULA PASIR PTH1KG</t>
   </si>
 </sst>
 </file>
@@ -754,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1136,21 +1148,21 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>57</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1159,18 +1171,18 @@
         <v>38</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1179,10 +1191,10 @@
         <v>38</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1199,7 +1211,7 @@
         <v>38</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>9</v>
@@ -1219,7 +1231,7 @@
         <v>38</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>9</v>
@@ -1239,10 +1251,10 @@
         <v>38</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1259,7 +1271,7 @@
         <v>38</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1279,10 +1291,10 @@
         <v>38</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1296,10 +1308,10 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>9</v>
@@ -1319,10 +1331,10 @@
         <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1339,7 +1351,7 @@
         <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>33</v>
@@ -1359,18 +1371,18 @@
         <v>12</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>82</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1379,10 +1391,10 @@
         <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>9</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1399,18 +1411,18 @@
         <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>87</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1419,10 +1431,10 @@
         <v>12</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1439,18 +1451,18 @@
         <v>12</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>92</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>94</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1459,30 +1471,30 @@
         <v>12</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1496,13 +1508,13 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1516,13 +1528,13 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1536,33 +1548,33 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1576,13 +1588,13 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1596,13 +1608,13 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1616,13 +1628,13 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1636,13 +1648,13 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1656,13 +1668,53 @@
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E46" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F45" s="1" t="s">
-        <v>60</v>
+      <c r="F46" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/MBG01D.xlsx
+++ b/MBG01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="126">
   <si>
     <t/>
   </si>
@@ -340,6 +340,15 @@
     <t>IDM GULA PRM KNG 1KG</t>
   </si>
   <si>
+    <t>20078902</t>
+  </si>
+  <si>
+    <t>INDOSUGAR GULA 1KG</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
+  </si>
+  <si>
     <t>20076765</t>
   </si>
   <si>
@@ -374,6 +383,12 @@
   </si>
   <si>
     <t>FS GULA PASIR PTH1KG</t>
+  </si>
+  <si>
+    <t>20134923</t>
+  </si>
+  <si>
+    <t>FS GULA PASIR HJU1KG</t>
   </si>
 </sst>
 </file>
@@ -766,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1614,15 +1629,15 @@
         <v>43</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>62</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -1639,10 +1654,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -1654,15 +1669,15 @@
         <v>50</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -1674,15 +1689,15 @@
         <v>54</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -1699,10 +1714,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -1711,10 +1726,50 @@
         <v>83</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/MBG01D.xlsx
+++ b/MBG01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="128">
   <si>
     <t/>
   </si>
@@ -377,6 +377,12 @@
   </si>
   <si>
     <t>LRST GULA KRSTL 1KG</t>
+  </si>
+  <si>
+    <t>20097781</t>
+  </si>
+  <si>
+    <t>KBA GULA KRSTL 1KG</t>
   </si>
   <si>
     <t>20103543</t>
@@ -781,7 +787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1746,7 +1752,7 @@
         <v>83</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -1766,9 +1772,29 @@
         <v>83</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F50" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/MBG01D.xlsx
+++ b/MBG01D.xlsx
@@ -11,24 +11,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="132">
   <si>
     <t/>
   </si>
   <si>
+    <t>20090009</t>
+  </si>
+  <si>
+    <t>SANIA BRS PRMIUM 5KG</t>
+  </si>
+  <si>
+    <t>MBG01D</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
     <t>20025487</t>
   </si>
   <si>
     <t>IDM RAMOS SUPER 5KG</t>
   </si>
   <si>
-    <t>MBG01D</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
+    <t>2</t>
   </si>
   <si>
     <t>20119956</t>
@@ -37,309 +46,342 @@
     <t>IDM BERAS KP.SPR 5KG</t>
   </si>
   <si>
-    <t>2</t>
+    <t>3</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
+    <t>20119830</t>
+  </si>
+  <si>
+    <t>LARST BRS SLYP SPR 5</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>20125752</t>
+  </si>
+  <si>
+    <t>BEFOOD STRA RMOS 5KG</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20062961</t>
+  </si>
+  <si>
+    <t>ANAKRAJA BRS KRSTL5K</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20142055</t>
+  </si>
+  <si>
+    <t>TOPI KOKI SETRA RYL5</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>10009392</t>
+  </si>
+  <si>
+    <t>W/A BRS S.SPR KPL 5</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20106876</t>
+  </si>
+  <si>
+    <t>UDG D/KOKI BRS PRM 5</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20097275</t>
+  </si>
+  <si>
+    <t>LAHAP BRS LELE 5KG</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20084982</t>
+  </si>
+  <si>
+    <t>D/KOKI BRAS SHT 5KG</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20142264</t>
+  </si>
+  <si>
+    <t>LAHAP LELE BRS PRM 5</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20128415</t>
+  </si>
+  <si>
+    <t>MED/SPHP BERAS 5KG</t>
+  </si>
+  <si>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20139532</t>
+  </si>
+  <si>
+    <t>A/R BRS KHS PLN WG5</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
     <t>20002897</t>
   </si>
   <si>
     <t>IDM PANDAN WANGI 5KG</t>
   </si>
   <si>
+    <t>20141056</t>
+  </si>
+  <si>
+    <t>SINTANUR PND WGI 5KG</t>
+  </si>
+  <si>
     <t>4</t>
   </si>
   <si>
-    <t>20125752</t>
-  </si>
-  <si>
-    <t>BEFOOD STRA RMOS 5KG</t>
+    <t>20142107</t>
+  </si>
+  <si>
+    <t>TAR BERAS KHUSUS 5KG</t>
+  </si>
+  <si>
+    <t>20142006</t>
+  </si>
+  <si>
+    <t>PTRI KOKI BRS KH 5KG</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20133809</t>
+  </si>
+  <si>
+    <t>DM NASI JAGUNG 250</t>
+  </si>
+  <si>
+    <t>20133810</t>
+  </si>
+  <si>
+    <t>DM NASI SINGKONG 250</t>
+  </si>
+  <si>
+    <t>20140704</t>
+  </si>
+  <si>
+    <t>IDM BRS PORANG 4X40G</t>
+  </si>
+  <si>
+    <t>20088559</t>
+  </si>
+  <si>
+    <t>IDM KETAN PUTIH 500G</t>
+  </si>
+  <si>
+    <t>20088561</t>
+  </si>
+  <si>
+    <t>IDM KETAN HITAM 500G</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20054184</t>
+  </si>
+  <si>
+    <t>IDM BERAS MERAH 2KG</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20141277</t>
+  </si>
+  <si>
+    <t>LARST BRS SLP SPR2.5</t>
+  </si>
+  <si>
+    <t>20000412</t>
+  </si>
+  <si>
+    <t>IDM KACANG HIJAU 500</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20061785</t>
+  </si>
+  <si>
+    <t>IDM POP CORN PCK200G</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20141513</t>
+  </si>
+  <si>
+    <t>IDM KCG TNH KPS 250G</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20134672</t>
+  </si>
+  <si>
+    <t>LRSST GL.KRSTAL 100S</t>
+  </si>
+  <si>
+    <t>TG,(E-1B)</t>
+  </si>
+  <si>
+    <t>20085279</t>
+  </si>
+  <si>
+    <t>IDM GULA PSR STK 30S</t>
+  </si>
+  <si>
+    <t>20085280</t>
+  </si>
+  <si>
+    <t>IDM GULA ARN STK 20S</t>
+  </si>
+  <si>
+    <t>20069092</t>
+  </si>
+  <si>
+    <t>IDM GULA BATU 225</t>
+  </si>
+  <si>
+    <t>20103654</t>
+  </si>
+  <si>
+    <t>IDM GL.AREN (KW) 200</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20121086</t>
+  </si>
+  <si>
+    <t>SUS GULA LKL KNG 1KG</t>
+  </si>
+  <si>
+    <t>TG,(E-2B)</t>
+  </si>
+  <si>
+    <t>20113564</t>
+  </si>
+  <si>
+    <t>GULAVIT GULA KRSTL 1</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>10021008</t>
+  </si>
+  <si>
+    <t>GULAKU GULA KUNG 1KG</t>
+  </si>
+  <si>
+    <t>10021010</t>
+  </si>
+  <si>
+    <t>GULAKU GULA PUTIH1KG</t>
+  </si>
+  <si>
+    <t>20042991</t>
+  </si>
+  <si>
+    <t>IDM GULA PSR PRM 1KG</t>
+  </si>
+  <si>
+    <t>20045854</t>
+  </si>
+  <si>
+    <t>PSM GULA PREMIUM 1KG</t>
+  </si>
+  <si>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20052296</t>
+  </si>
+  <si>
+    <t>IDM GULA PRM KNG 1KG</t>
+  </si>
+  <si>
+    <t>20076765</t>
+  </si>
+  <si>
+    <t>ROSE/B GULA PTH 1KG</t>
+  </si>
+  <si>
+    <t>20076768</t>
+  </si>
+  <si>
+    <t>ROSE/B GULA KNG 1KG</t>
+  </si>
+  <si>
+    <t>20078207</t>
+  </si>
+  <si>
+    <t>GMP GULA PASIR 1KG</t>
+  </si>
+  <si>
+    <t>20139024</t>
+  </si>
+  <si>
+    <t>LRST GULA KRSTL 500</t>
+  </si>
+  <si>
+    <t>20139025</t>
+  </si>
+  <si>
+    <t>LRST GULA KRSTL 1KG</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>20141056</t>
-  </si>
-  <si>
-    <t>SINTANUR PND WGI 5KG</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20062961</t>
-  </si>
-  <si>
-    <t>ANAKRAJA BRS KRSTL5K</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20142055</t>
-  </si>
-  <si>
-    <t>TOPI KOKI SETRA RYL5</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20142107</t>
-  </si>
-  <si>
-    <t>TAR BERAS KHUSUS 5KG</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20142006</t>
-  </si>
-  <si>
-    <t>PTRI KOKI BRS KH 5KG</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20128415</t>
-  </si>
-  <si>
-    <t>MED/SPHP BERAS 5KG</t>
-  </si>
-  <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20090009</t>
-  </si>
-  <si>
-    <t>SANIA BRS PRMIUM 5KG</t>
-  </si>
-  <si>
-    <t>10009392</t>
-  </si>
-  <si>
-    <t>W/A BRS S.SPR KPL 5</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20097275</t>
-  </si>
-  <si>
-    <t>LAHAP BRS LELE 5KG</t>
-  </si>
-  <si>
-    <t>20119830</t>
-  </si>
-  <si>
-    <t>LARST BRS SLYP SPR 5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20139532</t>
-  </si>
-  <si>
-    <t>A/R BRS KHS PLN WG5</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20106876</t>
-  </si>
-  <si>
-    <t>UDG D/KOKI BRS PRM 5</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20084982</t>
-  </si>
-  <si>
-    <t>D/KOKI BRAS SHT 5KG</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20142264</t>
-  </si>
-  <si>
-    <t>LAHAP LELE BRS PRM 5</t>
-  </si>
-  <si>
-    <t>20000412</t>
-  </si>
-  <si>
-    <t>IDM KACANG HIJAU 500</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20061785</t>
-  </si>
-  <si>
-    <t>IDM POP CORN PCK200G</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20133809</t>
-  </si>
-  <si>
-    <t>DM NASI JAGUNG 250</t>
-  </si>
-  <si>
-    <t>20133810</t>
-  </si>
-  <si>
-    <t>DM NASI SINGKONG 250</t>
-  </si>
-  <si>
-    <t>20140704</t>
-  </si>
-  <si>
-    <t>IDM BRS PORANG 4X40G</t>
-  </si>
-  <si>
-    <t>20088559</t>
-  </si>
-  <si>
-    <t>IDM KETAN PUTIH 500G</t>
-  </si>
-  <si>
-    <t>20054184</t>
-  </si>
-  <si>
-    <t>IDM BERAS MERAH 2KG</t>
-  </si>
-  <si>
-    <t>20141277</t>
-  </si>
-  <si>
-    <t>LARST BRS SLP SPR2.5</t>
-  </si>
-  <si>
-    <t>20141513</t>
-  </si>
-  <si>
-    <t>IDM KCG TNH KPS 250G</t>
-  </si>
-  <si>
-    <t>20085279</t>
-  </si>
-  <si>
-    <t>IDM GULA PSR STK 30S</t>
-  </si>
-  <si>
-    <t>20085280</t>
-  </si>
-  <si>
-    <t>IDM GULA ARN STK 20S</t>
-  </si>
-  <si>
-    <t>20134672</t>
-  </si>
-  <si>
-    <t>LRSST GL.KRSTAL 100S</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>TG,(E-1B)</t>
-  </si>
-  <si>
-    <t>20069092</t>
-  </si>
-  <si>
-    <t>IDM GULA BATU 225</t>
-  </si>
-  <si>
-    <t>20103654</t>
-  </si>
-  <si>
-    <t>IDM GL.AREN (KW) 200</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20088561</t>
-  </si>
-  <si>
-    <t>IDM KETAN HITAM 500G</t>
-  </si>
-  <si>
-    <t>20121086</t>
-  </si>
-  <si>
-    <t>SUS GULA LKL KNG 1KG</t>
-  </si>
-  <si>
-    <t>TG,(E-2B)</t>
-  </si>
-  <si>
-    <t>20113564</t>
-  </si>
-  <si>
-    <t>GULAVIT GULA KRSTL 1</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>10021008</t>
-  </si>
-  <si>
-    <t>GULAKU GULA KUNG 1KG</t>
-  </si>
-  <si>
-    <t>10021010</t>
-  </si>
-  <si>
-    <t>GULAKU GULA PUTIH1KG</t>
-  </si>
-  <si>
-    <t>20042991</t>
-  </si>
-  <si>
-    <t>IDM GULA PSR PRM 1KG</t>
-  </si>
-  <si>
-    <t>20045854</t>
-  </si>
-  <si>
-    <t>PSM GULA PREMIUM 1KG</t>
-  </si>
-  <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20052296</t>
-  </si>
-  <si>
-    <t>IDM GULA PRM KNG 1KG</t>
-  </si>
-  <si>
     <t>20078902</t>
   </si>
   <si>
@@ -347,36 +389,6 @@
   </si>
   <si>
     <t>,(E-1B)</t>
-  </si>
-  <si>
-    <t>20076765</t>
-  </si>
-  <si>
-    <t>ROSE/B GULA PTH 1KG</t>
-  </si>
-  <si>
-    <t>20076768</t>
-  </si>
-  <si>
-    <t>ROSE/B GULA KNG 1KG</t>
-  </si>
-  <si>
-    <t>20078207</t>
-  </si>
-  <si>
-    <t>GMP GULA PASIR 1KG</t>
-  </si>
-  <si>
-    <t>20139024</t>
-  </si>
-  <si>
-    <t>LRST GULA KRSTL 500</t>
-  </si>
-  <si>
-    <t>20139025</t>
-  </si>
-  <si>
-    <t>LRST GULA KRSTL 1KG</t>
   </si>
   <si>
     <t>20097781</t>
@@ -855,15 +867,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -872,10 +884,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -895,7 +907,7 @@
         <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -915,7 +927,7 @@
         <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -955,7 +967,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -975,7 +987,7 @@
         <v>27</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -995,44 +1007,44 @@
         <v>30</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -1040,19 +1052,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1060,10 +1072,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1072,18 +1084,18 @@
         <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1092,18 +1104,18 @@
         <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1112,18 +1124,18 @@
         <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1132,10 +1144,10 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1152,18 +1164,18 @@
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1172,10 +1184,10 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1189,110 +1201,110 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>12</v>
+        <v>56</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="F24" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1309,13 +1321,13 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1329,427 +1341,427 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>33</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="E32" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F32" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>5</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>18</v>
+        <v>99</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>62</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>15</v>
+        <v>122</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>62</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>21</v>
@@ -1760,16 +1772,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>24</v>
@@ -1780,22 +1792,22 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>27</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/MBG01D.xlsx
+++ b/MBG01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="124">
   <si>
     <t/>
   </si>
@@ -232,108 +232,87 @@
     <t>LARST BRS SLP SPR2.5</t>
   </si>
   <si>
-    <t>20000412</t>
-  </si>
-  <si>
-    <t>IDM KACANG HIJAU 500</t>
+    <t>20134672</t>
+  </si>
+  <si>
+    <t>LRSST GL.KRSTAL 100S</t>
+  </si>
+  <si>
+    <t>TG,(E-1B)</t>
+  </si>
+  <si>
+    <t>20085279</t>
+  </si>
+  <si>
+    <t>IDM GULA PSR STK 30S</t>
+  </si>
+  <si>
+    <t>20085280</t>
+  </si>
+  <si>
+    <t>IDM GULA ARN STK 20S</t>
+  </si>
+  <si>
+    <t>20069092</t>
+  </si>
+  <si>
+    <t>IDM GULA BATU 225</t>
+  </si>
+  <si>
+    <t>20103654</t>
+  </si>
+  <si>
+    <t>IDM GL.AREN (KW) 200</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20121086</t>
+  </si>
+  <si>
+    <t>SUS GULA LKL KNG 1KG</t>
+  </si>
+  <si>
+    <t>TG,(E-2B)</t>
+  </si>
+  <si>
+    <t>20113564</t>
+  </si>
+  <si>
+    <t>GULAVIT GULA KRSTL 1</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
+  </si>
+  <si>
+    <t>10021008</t>
+  </si>
+  <si>
+    <t>GULAKU GULA KUNG 1KG</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10021010</t>
+  </si>
+  <si>
+    <t>GULAKU GULA PUTIH1KG</t>
+  </si>
+  <si>
+    <t>20042991</t>
+  </si>
+  <si>
+    <t>IDM GULA PSR PRM 1KG</t>
   </si>
   <si>
     <t>PT,(E-2B)</t>
   </si>
   <si>
-    <t>20061785</t>
-  </si>
-  <si>
-    <t>IDM POP CORN PCK200G</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20141513</t>
-  </si>
-  <si>
-    <t>IDM KCG TNH KPS 250G</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20134672</t>
-  </si>
-  <si>
-    <t>LRSST GL.KRSTAL 100S</t>
-  </si>
-  <si>
-    <t>TG,(E-1B)</t>
-  </si>
-  <si>
-    <t>20085279</t>
-  </si>
-  <si>
-    <t>IDM GULA PSR STK 30S</t>
-  </si>
-  <si>
-    <t>20085280</t>
-  </si>
-  <si>
-    <t>IDM GULA ARN STK 20S</t>
-  </si>
-  <si>
-    <t>20069092</t>
-  </si>
-  <si>
-    <t>IDM GULA BATU 225</t>
-  </si>
-  <si>
-    <t>20103654</t>
-  </si>
-  <si>
-    <t>IDM GL.AREN (KW) 200</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20121086</t>
-  </si>
-  <si>
-    <t>SUS GULA LKL KNG 1KG</t>
-  </si>
-  <si>
-    <t>TG,(E-2B)</t>
-  </si>
-  <si>
-    <t>20113564</t>
-  </si>
-  <si>
-    <t>GULAVIT GULA KRSTL 1</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>RT,(E-6B)</t>
-  </si>
-  <si>
-    <t>10021008</t>
-  </si>
-  <si>
-    <t>GULAKU GULA KUNG 1KG</t>
-  </si>
-  <si>
-    <t>10021010</t>
-  </si>
-  <si>
-    <t>GULAKU GULA PUTIH1KG</t>
-  </si>
-  <si>
-    <t>20042991</t>
-  </si>
-  <si>
-    <t>IDM GULA PSR PRM 1KG</t>
-  </si>
-  <si>
     <t>20045854</t>
   </si>
   <si>
@@ -386,9 +365,6 @@
   </si>
   <si>
     <t>INDOSUGAR GULA 1KG</t>
-  </si>
-  <si>
-    <t>,(E-1B)</t>
   </si>
   <si>
     <t>20097781</t>
@@ -799,7 +775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1341,10 +1317,10 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>75</v>
@@ -1361,41 +1337,41 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1404,18 +1380,18 @@
         <v>51</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1424,18 +1400,18 @@
         <v>51</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1444,18 +1420,18 @@
         <v>51</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>90</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1464,50 +1440,50 @@
         <v>51</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>12</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1521,33 +1497,33 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1564,10 +1540,10 @@
         <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1584,10 +1560,10 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1604,19 +1580,19 @@
         <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
@@ -1624,19 +1600,19 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
@@ -1644,30 +1620,30 @@
         <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C43" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="F43" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -1684,10 +1660,10 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -1704,10 +1680,10 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>99</v>
+        <v>21</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1724,19 +1700,19 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B47" s="1" t="s">
-        <v>124</v>
-      </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
@@ -1744,69 +1720,9 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F50" s="1" t="s">
         <v>12</v>
       </c>
     </row>

--- a/MBG01D.xlsx
+++ b/MBG01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="122">
   <si>
     <t/>
   </si>
@@ -377,12 +377,6 @@
   </si>
   <si>
     <t>FS GULA PASIR PTH1KG</t>
-  </si>
-  <si>
-    <t>20134923</t>
-  </si>
-  <si>
-    <t>FS GULA PASIR HJU1KG</t>
   </si>
 </sst>
 </file>
@@ -775,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1706,26 +1700,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/MBG01D.xlsx
+++ b/MBG01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="128">
   <si>
     <t/>
   </si>
@@ -134,6 +134,24 @@
   </si>
   <si>
     <t>19</t>
+  </si>
+  <si>
+    <t>20128129</t>
+  </si>
+  <si>
+    <t>PUNO/K BERAS 5KG</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20143258</t>
+  </si>
+  <si>
+    <t>SI GEULIS BERAS5KG</t>
+  </si>
+  <si>
+    <t>21</t>
   </si>
   <si>
     <t>20128415</t>
@@ -769,7 +787,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1051,13 +1069,13 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1071,13 +1089,13 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1094,18 +1112,18 @@
         <v>8</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1114,18 +1132,18 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1134,7 +1152,7 @@
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>12</v>
@@ -1142,10 +1160,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1154,7 +1172,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>12</v>
@@ -1162,19 +1180,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>12</v>
@@ -1182,19 +1200,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>12</v>
@@ -1202,10 +1220,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1214,7 +1232,7 @@
         <v>11</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>12</v>
@@ -1222,10 +1240,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1234,18 +1252,18 @@
         <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1254,18 +1272,18 @@
         <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1274,7 +1292,7 @@
         <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1294,130 +1312,130 @@
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>21</v>
+        <v>73</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
+        <v>76</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1431,61 +1449,61 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F34" s="1" t="s">
         <v>93</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F35" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1494,18 +1512,18 @@
         <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1514,10 +1532,10 @@
         <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1534,18 +1552,18 @@
         <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -1554,18 +1572,18 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -1574,18 +1592,18 @@
         <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -1594,18 +1612,18 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -1614,18 +1632,18 @@
         <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -1634,18 +1652,18 @@
         <v>15</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>94</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -1654,18 +1672,18 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>18</v>
+        <v>96</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>12</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -1674,18 +1692,18 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -1694,9 +1712,49 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F48" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/MBG01D.xlsx
+++ b/MBG01D.xlsx
@@ -190,7 +190,7 @@
     <t>20142107</t>
   </si>
   <si>
-    <t>TAR BERAS KHUSUS 5KG</t>
+    <t>ARN BERAS KHUSUS 5KG</t>
   </si>
   <si>
     <t>20142006</t>

--- a/MBG01D.xlsx
+++ b/MBG01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="131">
   <si>
     <t/>
   </si>
@@ -152,6 +152,15 @@
   </si>
   <si>
     <t>21</t>
+  </si>
+  <si>
+    <t>20142056</t>
+  </si>
+  <si>
+    <t>NASIKU/B BERAS PRM 5</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
   <si>
     <t>20128415</t>
@@ -787,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1109,13 +1118,13 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1132,7 +1141,7 @@
         <v>8</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>52</v>
@@ -1152,18 +1161,18 @@
         <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1172,7 +1181,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>12</v>
@@ -1192,7 +1201,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>12</v>
@@ -1200,10 +1209,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1212,7 +1221,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>12</v>
@@ -1229,10 +1238,10 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>12</v>
@@ -1240,10 +1249,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1252,7 +1261,7 @@
         <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>12</v>
@@ -1260,10 +1269,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1272,7 +1281,7 @@
         <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>12</v>
@@ -1280,10 +1289,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1292,18 +1301,18 @@
         <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1312,7 +1321,7 @@
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1352,30 +1361,30 @@
         <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1389,73 +1398,73 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>12</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1469,7 +1478,7 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>76</v>
@@ -1489,30 +1498,30 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="E35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="C36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>100</v>
@@ -1532,18 +1541,18 @@
         <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -1552,10 +1561,10 @@
         <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1572,7 +1581,7 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>108</v>
@@ -1592,18 +1601,18 @@
         <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -1612,18 +1621,18 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -1632,18 +1641,18 @@
         <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -1655,15 +1664,15 @@
         <v>76</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -1672,18 +1681,18 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>100</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -1692,10 +1701,10 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1712,18 +1721,18 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>12</v>
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -1732,18 +1741,18 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -1752,9 +1761,29 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F49" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/MBG01D.xlsx
+++ b/MBG01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="137">
   <si>
     <t/>
   </si>
@@ -161,6 +161,24 @@
   </si>
   <si>
     <t>22</t>
+  </si>
+  <si>
+    <t>20139555</t>
+  </si>
+  <si>
+    <t>PNKWN BERAS PRMIUM10</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20143145</t>
+  </si>
+  <si>
+    <t>LHP LELE PREM 10 KG</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
   <si>
     <t>20128415</t>
@@ -796,7 +814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1138,13 +1156,13 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1158,13 +1176,13 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1181,18 +1199,18 @@
         <v>8</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1201,18 +1219,18 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1221,7 +1239,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>12</v>
@@ -1229,10 +1247,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1241,7 +1259,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>12</v>
@@ -1249,19 +1267,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>12</v>
@@ -1269,19 +1287,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>12</v>
@@ -1289,10 +1307,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1301,7 +1319,7 @@
         <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>12</v>
@@ -1309,10 +1327,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1321,18 +1339,18 @@
         <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1341,18 +1359,18 @@
         <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1361,7 +1379,7 @@
         <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1381,130 +1399,130 @@
         <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>93</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>79</v>
+        <v>15</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>96</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1518,61 +1536,61 @@
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="C37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F37" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="C38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F38" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -1581,18 +1599,18 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -1601,10 +1619,10 @@
         <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>60</v>
+        <v>8</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1621,18 +1639,18 @@
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -1641,18 +1659,18 @@
         <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -1661,18 +1679,18 @@
         <v>15</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -1681,18 +1699,18 @@
         <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -1701,18 +1719,18 @@
         <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -1721,18 +1739,18 @@
         <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -1741,18 +1759,18 @@
         <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -1761,18 +1779,18 @@
         <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>21</v>
+        <v>130</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -1781,9 +1799,49 @@
         <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F51" s="1" t="s">
         <v>5</v>
       </c>
     </row>
